--- a/wk3/ten_tips_for_charts.xlsx
+++ b/wk3/ten_tips_for_charts.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E8A3DDB-4D9C-4155-9C4F-40088254241A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB22C1C1-FD43-EB49-A65C-B496051CD1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="10" xr2:uid="{53C78ED7-DDA0-4AE4-BCF6-674254D8C7B1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="16060" activeTab="11" xr2:uid="{53C78ED7-DDA0-4AE4-BCF6-674254D8C7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="2" r:id="rId1"/>
@@ -25,6 +25,41 @@
     <definedName name="_56F9DC9755BA473782653E2940F9FormId">"v4j5cvGGr0GRqy180BHbR3RTh83xGnJEukQfvKTbAtxUNTNKN09GODJOMVI2OTJWUUYyMERWNEZHUy4u"</definedName>
     <definedName name="_56F9DC9755BA473782653E2940F9ResponseSheet">"Form1"</definedName>
     <definedName name="_56F9DC9755BA473782653E2940F9SourceDocId">"{b0655248-1b15-479e-8bea-90faffef96f4}"</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'1'!$B$13:$B$16</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'1'!$C$12</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'4'!$D$102:$G$102</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'4'!$D$103:$G$103</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'4'!$D$104:$G$104</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'4'!$D$105:$G$105</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'7'!$G$13:$G$18</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'7'!$H$12</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'7'!$H$13:$H$18</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'7'!$I$12</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'7'!$I$13:$I$18</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'7'!$G$13:$G$18</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'1'!$C$13:$C$16</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'7'!$H$12</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'7'!$H$13:$H$18</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'7'!$I$12</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'7'!$I$13:$I$18</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">'7'!$G$13:$G$18</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">'7'!$H$12</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">'7'!$H$13:$H$18</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">'7'!$I$12</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">'7'!$I$13:$I$18</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">'9'!$F$13:$F$18</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'4'!$C$101</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">'9'!$G$12</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">'9'!$G$13:$G$18</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">'9'!$F$13:$F$18</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">'9'!$G$12</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'9'!$G$13:$G$18</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'4'!$C$102</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'4'!$C$103</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'4'!$C$104</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'4'!$C$105</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'4'!$D$100:$G$100</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'4'!$D$101:$G$101</definedName>
     <definedName name="grp_Brace">"Another bracket line,Bracket line"</definedName>
     <definedName name="grp_MoreInfo">"Bottom line,Group 113"</definedName>
     <definedName name="grp_Practice">'10'!$A$1</definedName>
@@ -33,6 +68,9 @@
     <definedName name="SalesTax">0.0825</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="12" r:id="rId13"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -52,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
   <si>
     <t>Welcome
 Instructions for screen readers: After you go through the tip sheets in this tutorial, you'll learn how to quickly master chart elements. The instructions for each sheet start in cell A1, and each subsequent step is in cell A2, A3, and so on. 
@@ -168,6 +206,21 @@
   </si>
   <si>
     <t>2) Press ALT+H+FD+P top launch the Selection pane, then use your TAB and Arrow keys to navigate to the chart in question. Next, press ALT+JC+C to launch the Change Chart Type dialog. Pie will be selected, so you can press the Tab key twice, then Right Arrow to select the Pie of Pie option. Press enter to confirm your selection.</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Fruits</t>
+  </si>
+  <si>
+    <t>Vegetables</t>
   </si>
 </sst>
 </file>
@@ -372,7 +425,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1">
       <alignment wrapText="1"/>
@@ -442,6 +495,13 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="3" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Comma 2" xfId="8" xr:uid="{40914702-D8DC-4946-B353-1B85F17502B9}"/>
@@ -454,7 +514,14 @@
     <cellStyle name="Title 2" xfId="3" xr:uid="{7CFBCD2A-9F84-449D-B456-22B4A1CFB6F6}"/>
     <cellStyle name="z A Column text" xfId="7" xr:uid="{8335E534-3B51-4BEF-8D04-F835BAC8E001}"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -509,8 +576,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="CustomTableStyle" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -525,6 +592,1418 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'1'!$C$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Amount sold</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'1'!$B$13:$B$16</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Kelly</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dave</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Brian</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sally</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'1'!$C$13:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1A4E-0949-AC14-21BA473CA997}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="2065004095"/>
+        <c:axId val="2064990207"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2065004095"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2064990207"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2064990207"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2065004095"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'9'!$G$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Amount</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:explosion val="35"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'9'!$F$13:$F$18</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Apples</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pears</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Grapes</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Kiwis</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oranges</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Plums</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'9'!$G$13:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C0D9-4A47-A071-CD0D10036397}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10'!$B$101</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Kelly</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'10'!$C$100:$F$100</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'10'!$C$101:$F$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1937-47B6-B92B-FB28E7199254}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10'!$B$102</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dave</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'10'!$C$100:$F$100</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'10'!$C$102:$F$102</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>523</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1937-47B6-B92B-FB28E7199254}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10'!$B$103</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Brian</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'10'!$C$100:$F$100</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'10'!$C$103:$F$103</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1937-47B6-B92B-FB28E7199254}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="651751360"/>
+        <c:axId val="651749720"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="651751360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="651749720"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="651749720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="651751360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2'!$D$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Commission</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2'!$B$13:$B$16</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Kelly</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dave</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Brian</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sally</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2'!$D$13:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-29B2-FE42-90BD-C814D9DB9ACC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="2064884031"/>
+        <c:axId val="1970552127"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2064884031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1970552127"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1970552127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2064884031"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -675,6 +2154,71 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'3'!$F$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'3'!$C$14:$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Kelly</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dave</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Brian</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'3'!$F$14:$F$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C825-9944-B4FC-1E646603C868}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -877,7 +2421,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -891,7 +2435,37 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:areaChart>
@@ -1330,6 +2904,36 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1387,7 +2991,7 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr rtl="0">
+          <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -1441,7 +3045,398 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[ten_tips_for_charts.xlsx]5!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5'!$G$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5'!$F$14:$F$16</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Apples</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oranges</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'5'!$G$14:$G$16</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C6FA-DE48-AE5E-664B2B722805}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1970994495"/>
+        <c:axId val="2032895743"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1970994495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2032895743"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2032895743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1970994495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1487,27 +3482,37 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
-              <c:f>'6'!$H$14:$H$18</c:f>
-              <c:strCache>
+            <c:multiLvlStrRef>
+              <c:f>'6'!$G$14:$H$18</c:f>
+              <c:multiLvlStrCache>
                 <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Apples</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Oranges</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Bananas</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Asparagus</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Broccoli</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Apples</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Oranges</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Bananas</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Asparagus</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Broccoli</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Fruits</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Vegetables</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1684,7 +3689,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1789,6 +3794,21 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="499528176"/>
+        <c:axId val="499528504"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -1804,15 +3824,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:numRef>
               <c:f>'7'!$G$13:$G$18</c:f>
@@ -1867,6 +3889,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-0E2C-4E79-BD04-4A3FCF594E7D}"/>
@@ -1881,10 +3904,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:axId val="499528176"/>
-        <c:axId val="499528504"/>
-      </c:barChart>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1963306367"/>
+        <c:axId val="1970990015"/>
+      </c:lineChart>
       <c:dateAx>
         <c:axId val="499528176"/>
         <c:scaling>
@@ -1991,6 +4015,64 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:valAx>
+        <c:axId val="1970990015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1963306367"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dateAx>
+        <c:axId val="1963306367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="[$-409]d\-mmm;@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1970990015"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2074,7 +4156,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2109,7 +4191,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Chart Title</a:t>
+              <a:t>Week</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> 1</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2554,7 +4640,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2587,6 +4673,7 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:explosion val="80"/>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
@@ -2867,457 +4954,87 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'10'!$B$101</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Kelly</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'10'!$C$100:$F$100</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Feb</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Apr</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'10'!$C$101:$F$101</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>800</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1400</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1500</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1937-47B6-B92B-FB28E7199254}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'10'!$B$102</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Dave</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'10'!$C$100:$F$100</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Feb</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Apr</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'10'!$C$102:$F$102</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>350</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>523</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1937-47B6-B92B-FB28E7199254}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'10'!$B$103</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Brian</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'10'!$C$100:$F$100</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Feb</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Apr</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'10'!$C$103:$F$103</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>600</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>800</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1937-47B6-B92B-FB28E7199254}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="651751360"/>
-        <c:axId val="651749720"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="651751360"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="651749720"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="651749720"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="651751360"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3597,7 +5314,1122 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4101,7 +6933,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -4305,22 +7137,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -4425,8 +7258,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -4558,19 +7391,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -7118,6 +9952,1012 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
@@ -9633,6 +13473,42 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4AE7157-CD91-8A57-80BF-DBABF9304BEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -15986,6 +19862,42 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14311A34-069A-2378-795E-B9B50C4B210B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -18108,6 +22020,42 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{179BC854-16D8-AEB6-BB0D-8F38B711ECFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -22679,16 +26627,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>8189</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>188460</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>427288</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>36060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>183673</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>109360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -22710,8 +26658,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3103814" y="1331460"/>
-          <a:ext cx="175484" cy="173490"/>
+          <a:off x="10866688" y="798060"/>
+          <a:ext cx="652211" cy="644800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22734,7 +26682,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>352043</xdr:colOff>
+      <xdr:colOff>288543</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>96012</xdr:rowOff>
     </xdr:to>
@@ -23347,7 +27295,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
+      <xdr:colOff>676275</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>55140</xdr:rowOff>
     </xdr:to>
@@ -24196,7 +28144,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>352043</xdr:colOff>
+      <xdr:colOff>288543</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>21336</xdr:rowOff>
     </xdr:to>
@@ -24370,13 +28318,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>565150</xdr:colOff>
+      <xdr:colOff>501650</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>155448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>38608</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>826008</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>131064</xdr:rowOff>
     </xdr:to>
@@ -24718,13 +28666,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>760123</xdr:colOff>
+      <xdr:colOff>683923</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>17040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>258727</xdr:colOff>
+      <xdr:colOff>195227</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>10944</xdr:rowOff>
     </xdr:to>
@@ -24884,13 +28832,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>275837</xdr:colOff>
+      <xdr:colOff>212337</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>17040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>325367</xdr:colOff>
+      <xdr:colOff>261867</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>55140</xdr:rowOff>
     </xdr:to>
@@ -25525,6 +29473,42 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1054100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD19FD26-23A6-05EE-0A56-422CD76A2585}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -33239,11 +37223,119 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Author" refreshedDate="46314.503476620368" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="5" xr:uid="{6B6DB0BB-7EAB-004D-AA90-5B66B88F1832}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="tbl_pvtchrts"/>
+  </cacheSource>
+  <cacheFields count="2">
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Apples"/>
+        <s v="Oranges"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="200" maxValue="1000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="5">
+  <r>
+    <x v="0"/>
+    <n v="500"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="800"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="800"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="200"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A8765EF3-7366-0540-857A-3BA86E6D7FEB}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="1" baseField="0" baseItem="0" numFmtId="1"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2CF44F44-6583-4ED5-A449-4119FF501C34}" name="RecommendedChartData" displayName="RecommendedChartData" ref="B12:C16" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6E1FC270-3EE1-4FF1-8490-B832AF259C7D}" name="Salesperson"/>
-    <tableColumn id="2" xr3:uid="{ABD5AAA2-5FC1-42C3-88E8-54DF572DDBA7}" name="Amount sold" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{ABD5AAA2-5FC1-42C3-88E8-54DF572DDBA7}" name="Amount sold" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="CustomTableStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33258,8 +37350,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27414BAC-ACF8-43CE-A8CA-F68415D658EC}" name="RecommendedChartData3" displayName="RecommendedChartData3" ref="B12:D16" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{762FF5D1-22CC-4505-A7A7-4539A3917FDC}" name="Salesperson"/>
-    <tableColumn id="2" xr3:uid="{C606BD3E-9325-476A-A5AD-7C813C477619}" name="Sales" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{60151564-2A79-402B-81CE-765C4A7EDE57}" name="Commission" dataDxfId="8" dataCellStyle="Normal 2">
+    <tableColumn id="2" xr3:uid="{C606BD3E-9325-476A-A5AD-7C813C477619}" name="Sales" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{60151564-2A79-402B-81CE-765C4A7EDE57}" name="Commission" dataDxfId="9" dataCellStyle="Normal 2">
       <calculatedColumnFormula>0.05*RecommendedChartData3[[#This Row],[Sales]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -33273,7 +37365,21 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{F50737D3-9553-E24B-9180-33CEB3FB0A66}" name="Table1" displayName="Table1" ref="C13:F16" totalsRowShown="0" headerRowBorderDxfId="0" dataCellStyle="Normal 5 2 2">
+  <autoFilter ref="C13:F16" xr:uid="{F50737D3-9553-E24B-9180-33CEB3FB0A66}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{3F6E8892-E17A-CB40-BB3F-711DC4FE6637}" name="Salesperson" dataCellStyle="Normal 5 2 2"/>
+    <tableColumn id="2" xr3:uid="{68C2DBED-305A-2D48-A432-9E73CD57F05B}" name="Jan" dataCellStyle="Normal 5 2 2"/>
+    <tableColumn id="3" xr3:uid="{09449D74-5489-9743-9471-A82475206E47}" name="Feb" dataCellStyle="Normal 5 2 2"/>
+    <tableColumn id="4" xr3:uid="{40A10E9F-3798-3243-8905-4FE3D65F87FC}" name="Mar" dataCellStyle="Normal 5 2 2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CE5ECD12-E99C-41D4-837D-31C85FE31A2E}" name="Table4" displayName="Table4" ref="C100:G105" totalsRowShown="0">
+  <autoFilter ref="C100:G105" xr:uid="{CE5ECD12-E99C-41D4-837D-31C85FE31A2E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{BBCCB46F-1EDC-4311-A169-F0B553C173DD}" name="Salesperson"/>
     <tableColumn id="2" xr3:uid="{B344E005-2DF5-4594-BD01-8F06D59D3C67}" name="Jan"/>
@@ -33285,51 +37391,51 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF3102AB-6169-42B0-B1C1-FAE990390C09}" name="tbl_pvtchrts" displayName="tbl_pvtchrts" ref="B13:C18" totalsRowShown="0">
   <autoFilter ref="B13:C18" xr:uid="{00000000-0009-0000-0100-000016000000}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{874FDDCF-88F0-4DAA-A944-4D7168F383B0}" name="Product"/>
-    <tableColumn id="3" xr3:uid="{4CA54BFE-906D-4799-84EB-56A147451722}" name="Amount" dataDxfId="7"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A57D7224-3185-4ABB-A928-42872ECBD348}" name="tbl_secondaryaxis15" displayName="tbl_secondaryaxis15" ref="G12:I18" totalsRowShown="0">
-  <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{B499664A-B19C-4D2D-889C-FA866087B7A8}" name="Date" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{FB3FAF6C-C2EC-4CBD-8CFF-3DA5CB505E01}" name="Sales" dataDxfId="5" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{2A29CC9F-1389-4B6B-B07F-EEE50C5EADE9}" name="Profit %" dataDxfId="4" dataCellStyle="Normal 5 2 2"/>
+    <tableColumn id="3" xr3:uid="{4CA54BFE-906D-4799-84EB-56A147451722}" name="Amount" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A710BA4D-1C5C-4222-9C55-A031C171F343}" name="tbl_secondaryaxis6" displayName="tbl_secondaryaxis6" ref="G13:I18" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A57D7224-3185-4ABB-A928-42872ECBD348}" name="tbl_secondaryaxis15" displayName="tbl_secondaryaxis15" ref="G12:I18" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{82F72803-F37D-4392-AAC3-7C9CBC06B121}" name="Date" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{95020895-E079-4468-B59B-182899290B02}" name="Attendance" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{7BBA4995-0C2A-4D9E-98FA-EA30461ABA39}" name="Food sales" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{B499664A-B19C-4D2D-889C-FA866087B7A8}" name="Date" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{FB3FAF6C-C2EC-4CBD-8CFF-3DA5CB505E01}" name="Sales" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{2A29CC9F-1389-4B6B-B07F-EEE50C5EADE9}" name="Profit %" dataDxfId="5" dataCellStyle="Normal 5 2 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B200C274-2CCC-470E-B929-4418797DF727}" name="Table192122242526" displayName="Table192122242526" ref="F12:G18" totalsRowShown="0">
-  <autoFilter ref="F12:G18" xr:uid="{00000000-0009-0000-0100-000019000000}"/>
-  <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{97132582-3AD4-47A1-AF80-7692FC4E4093}" name="Product"/>
-    <tableColumn id="3" xr3:uid="{A130EAA5-A2DE-40E8-A3F9-71B78958BBF5}" name="Amount" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A710BA4D-1C5C-4222-9C55-A031C171F343}" name="tbl_secondaryaxis6" displayName="tbl_secondaryaxis6" ref="G13:I18" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="2" xr3:uid="{82F72803-F37D-4392-AAC3-7C9CBC06B121}" name="Date" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{95020895-E079-4468-B59B-182899290B02}" name="Attendance" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{7BBA4995-0C2A-4D9E-98FA-EA30461ABA39}" name="Food sales" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B200C274-2CCC-470E-B929-4418797DF727}" name="Table192122242526" displayName="Table192122242526" ref="F12:G18" totalsRowShown="0">
+  <autoFilter ref="F12:G18" xr:uid="{00000000-0009-0000-0100-000019000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="2" xr3:uid="{97132582-3AD4-47A1-AF80-7692FC4E4093}" name="Product"/>
+    <tableColumn id="3" xr3:uid="{A130EAA5-A2DE-40E8-A3F9-71B78958BBF5}" name="Amount" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{2D798D39-5D74-4174-A3A9-D60539BA7907}" name="Table410" displayName="Table410" ref="B100:F103" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{CC3A817C-01C3-43A5-97DF-FCF465001BCD}" name="Salesperson"/>
@@ -33644,29 +37750,29 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="115.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="11.109375" style="2"/>
+    <col min="1" max="1" width="115.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="11.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="63" x14ac:dyDescent="1.3">
+    <row r="2" spans="1:1" ht="62" x14ac:dyDescent="0.75">
       <c r="A2" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="44.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" ht="48" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="200.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
     </row>
   </sheetData>
@@ -33683,42 +37789,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6686533-C7FE-4B60-A7F0-CB6411E26A69}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="3" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F12" s="11" t="s">
         <v>16</v>
       </c>
@@ -33726,7 +37832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F13" s="12" t="s">
         <v>18</v>
       </c>
@@ -33734,7 +37840,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F14" s="12" t="s">
         <v>31</v>
       </c>
@@ -33742,7 +37848,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F15" s="12" t="s">
         <v>32</v>
       </c>
@@ -33750,7 +37856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="F16" s="12" t="s">
         <v>33</v>
       </c>
@@ -33758,7 +37864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F17" s="12" t="s">
         <v>19</v>
       </c>
@@ -33766,7 +37872,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F18" s="12" t="s">
         <v>34</v>
       </c>
@@ -33774,57 +37880,57 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
       <c r="L107" s="25"/>
@@ -33848,46 +37954,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D78B336-BF6D-4771-B5CD-EE5F7BCB6FCC}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:M110"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="3" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="10"/>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B100" s="11" t="s">
         <v>2</v>
       </c>
@@ -33904,7 +38010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B101" s="11" t="s">
         <v>4</v>
       </c>
@@ -33921,7 +38027,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B102" s="11" t="s">
         <v>5</v>
       </c>
@@ -33938,7 +38044,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B103" s="11" t="s">
         <v>6</v>
       </c>
@@ -33955,7 +38061,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
@@ -33963,29 +38069,29 @@
       <c r="L104" s="11"/>
       <c r="M104" s="11"/>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.2">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
       <c r="L105" s="11"/>
       <c r="M105" s="11"/>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.2">
       <c r="L106" s="11"/>
       <c r="M106" s="11"/>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.2">
       <c r="L107" s="11"/>
       <c r="M107" s="11"/>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.2">
       <c r="L108" s="11"/>
       <c r="M108" s="11"/>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.2">
       <c r="L109" s="11"/>
       <c r="M109" s="11"/>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.2">
       <c r="L110" s="11"/>
       <c r="M110" s="11"/>
     </row>
@@ -34015,35 +38121,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:B6"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.7" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="6"/>
-    <col min="2" max="2" width="95.109375" style="11" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="1" width="8.83203125" style="6"/>
+    <col min="2" max="2" width="95.1640625" style="11" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" s="36" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" s="36" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="11"/>
     </row>
-    <row r="3" spans="1:2" s="36" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" s="36" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:2" s="37" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" s="37" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21"/>
       <c r="B4" s="11"/>
     </row>
-    <row r="5" spans="1:2" s="38" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" s="38" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="11"/>
     </row>
-    <row r="6" spans="1:2" s="38" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" s="38" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="11"/>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="6">
+  <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Nice work. " sqref="A1" xr:uid="{5C4A7E09-EB82-4A4B-897D-0C8F25E6F70E}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Thanks for checking out the chart tips! Now check out these other links to help make you even more productive:" sqref="A2" xr:uid="{6700B25F-A827-4121-9BBE-A177DC32E721}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Learn more about charts_x000a_Take a look at this article for more details on creating charts." sqref="A3" xr:uid="{90BD2AB0-343A-4555-9C71-36C76E94F55A}"/>
@@ -34063,46 +38169,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7193D5-8253-4A58-B990-AD52407E3E4A}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="3" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="L9" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"Good job! You placed"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"your first column field."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"Click Next to continue..."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
         <v>2</v>
       </c>
@@ -34110,7 +38216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
         <v>4</v>
       </c>
@@ -34118,7 +38224,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>5</v>
       </c>
@@ -34126,7 +38232,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" s="12" t="s">
         <v>6</v>
       </c>
@@ -34134,7 +38240,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
@@ -34142,60 +38248,60 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="15"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34222,45 +38328,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{558CDC37-9CD8-48D1-939D-AFCE43F83555}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="2" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="2" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"Good job! You placed"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"your first column field."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"Click Next to continue..."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
         <v>2</v>
       </c>
@@ -34271,7 +38377,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
         <v>4</v>
       </c>
@@ -34283,7 +38389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>5</v>
       </c>
@@ -34295,7 +38401,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" s="12" t="s">
         <v>6</v>
       </c>
@@ -34307,7 +38413,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
@@ -34319,57 +38425,57 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34395,57 +38501,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA3EC7F-66B1-4143-BE9F-A02A63FC9037}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="2" width="4.109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" style="7" customWidth="1"/>
-    <col min="5" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="2" width="4.1640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="7" customWidth="1"/>
+    <col min="5" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10" t="str">
         <f>IF(AND($C$15="Buyer",$I$18=1175),"Good job! You placed"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10" t="str">
         <f>IF(AND($C$15="Buyer",$I$18=1175),"your first column field."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K11" s="10" t="str">
         <f>IF(AND($C$15="Buyer",$I$18=1175),"Click Next to continue..."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="18" t="s">
         <v>2</v>
       </c>
@@ -34455,8 +38561,11 @@
       <c r="E13" s="19" t="s">
         <v>11</v>
       </c>
+      <c r="F13" s="46" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="11" t="s">
         <v>4</v>
       </c>
@@ -34466,8 +38575,11 @@
       <c r="E14" s="11">
         <v>500</v>
       </c>
+      <c r="F14" s="45">
+        <v>600</v>
+      </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="11" t="s">
         <v>5</v>
       </c>
@@ -34477,8 +38589,11 @@
       <c r="E15" s="11">
         <v>800</v>
       </c>
+      <c r="F15" s="45">
+        <v>500</v>
+      </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C16" s="11" t="s">
         <v>6</v>
       </c>
@@ -34488,63 +38603,66 @@
       <c r="E16" s="11">
         <v>1000</v>
       </c>
+      <c r="F16" s="45">
+        <v>700</v>
+      </c>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34560,6 +38678,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -34567,66 +38688,66 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A9FCD3-95CA-48E4-B341-6706423068E4}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:O107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="2" width="4.109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" style="7" customWidth="1"/>
-    <col min="5" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="2" width="4.1640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="7" customWidth="1"/>
+    <col min="5" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O3" s="20"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O4" s="20"/>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O5" s="20"/>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7"/>
       <c r="O7" s="20"/>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10" t="str">
         <f>IF(AND($C$102="Buyer",$I$18=1175),"Good job! You placed"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10" t="str">
         <f>IF(AND($C$102="Buyer",$I$18=1175),"your first column field."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="10" t="str">
         <f>IF(AND($C$102="Buyer",$I$18=1175),"Click Next to continue..."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11" t="s">
         <v>2</v>
@@ -34644,7 +38765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11" t="s">
         <v>4</v>
@@ -34662,7 +38783,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11" t="s">
         <v>5</v>
@@ -34680,7 +38801,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11" t="s">
         <v>6</v>
@@ -34698,7 +38819,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B104" s="11"/>
       <c r="C104" s="11" t="s">
         <v>7</v>
@@ -34716,7 +38837,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C105" s="7" t="s">
         <v>14</v>
       </c>
@@ -34733,11 +38854,11 @@
         <v>988</v>
       </c>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34763,207 +38884,263 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52595332-3061-4A1A-A433-FAE60639EA6B}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="11.109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="3" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.1640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="F13" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="39">
         <v>500</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="F14" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="47">
+        <v>2100</v>
+      </c>
+      <c r="H14"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="39">
         <v>800</v>
       </c>
-      <c r="H15" s="11"/>
+      <c r="F15" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="47">
+        <v>1200</v>
+      </c>
+      <c r="H15"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="40">
         <v>800</v>
       </c>
-      <c r="H16" s="11"/>
+      <c r="F16" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="47">
+        <v>3300</v>
+      </c>
+      <c r="H16"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="39">
         <v>1000</v>
       </c>
-      <c r="H17" s="11"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="39">
         <v>200</v>
       </c>
-      <c r="H18" s="11"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H19" s="11"/>
+    <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H20" s="11"/>
+    <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H21" s="11"/>
+    <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H22" s="11"/>
+    <row r="22" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H23" s="11"/>
+    <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H24" s="11"/>
+    <row r="24" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H25" s="11"/>
+    <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H26" s="11"/>
+    <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="11"/>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="11"/>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="11"/>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34977,10 +39154,10 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="To continue with this tutorial, press CTRL+PAGE DOWN. To go to the previous sheet, press CTRL+PAGE UP." sqref="A7" xr:uid="{AD13F0B7-C570-4767-8BC6-CFAFD316C7EA}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -34989,38 +39166,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C08892-693F-4163-9FFB-B7A94019F9E0}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:L106"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="11.109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="3" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11.1640625" style="7" customWidth="1"/>
     <col min="7" max="7" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="8" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="10"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G13" s="23" t="s">
         <v>20</v>
       </c>
@@ -35031,8 +39208,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G14" s="25"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G14" s="25" t="s">
+        <v>40</v>
+      </c>
       <c r="H14" s="25" t="s">
         <v>18</v>
       </c>
@@ -35040,7 +39219,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="26"/>
       <c r="H15" s="26" t="s">
         <v>19</v>
@@ -35049,7 +39228,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G16" s="25"/>
       <c r="H16" s="27" t="s">
         <v>21</v>
@@ -35058,8 +39237,10 @@
         <v>800</v>
       </c>
     </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G17" s="26"/>
+    <row r="17" spans="7:9" x14ac:dyDescent="0.2">
+      <c r="G17" s="26" t="s">
+        <v>41</v>
+      </c>
       <c r="H17" s="28" t="s">
         <v>22</v>
       </c>
@@ -35067,7 +39248,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G18" s="25"/>
       <c r="H18" s="25" t="s">
         <v>23</v>
@@ -35076,57 +39257,57 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
@@ -35150,40 +39331,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4871CEE6-57A7-4C76-B5A9-FF1C03A53814}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="11.109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="3" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="11.1640625" style="7" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.109375" style="7" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="7"/>
+    <col min="9" max="10" width="11.1640625" style="7" customWidth="1"/>
+    <col min="11" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G12" s="22" t="s">
         <v>25</v>
       </c>
@@ -35194,7 +39375,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G13" s="31">
         <v>43101</v>
       </c>
@@ -35205,7 +39386,7 @@
         <v>0.33754898404938316</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G14" s="31">
         <v>43102</v>
       </c>
@@ -35216,7 +39397,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="31">
         <v>43103</v>
       </c>
@@ -35227,7 +39408,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G16" s="31">
         <v>43104</v>
       </c>
@@ -35238,7 +39419,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G17" s="31">
         <v>43105</v>
       </c>
@@ -35249,7 +39430,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G18" s="31">
         <v>43106</v>
       </c>
@@ -35260,57 +39441,57 @@
         <v>0.23900536726791932</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -35335,40 +39516,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E34304-B7D8-4D3F-BF66-6C20E68C384F}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:L108"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.1640625" style="6"/>
+    <col min="2" max="3" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.1640625" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G12" s="34" t="s">
         <v>27</v>
       </c>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G13" s="22" t="s">
         <v>25</v>
       </c>
@@ -35379,7 +39560,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G14" s="35">
         <v>43101</v>
       </c>
@@ -35390,7 +39571,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="35">
         <v>43102</v>
       </c>
@@ -35401,7 +39582,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G16" s="35">
         <v>43103</v>
       </c>
@@ -35412,7 +39593,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G17" s="35">
         <v>43104</v>
       </c>
@@ -35423,7 +39604,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G18" s="35">
         <v>43105</v>
       </c>
@@ -35434,57 +39615,57 @@
         <v>900</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D108" s="11"/>
       <c r="E108" s="11"/>
     </row>
